--- a/branches/release/v2027.0.0-ballot/ValueSet-mii-vs-consent-policy.xlsx
+++ b/branches/release/v2027.0.0-ballot/ValueSet-mii-vs-consent-policy.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:39:54+00:00</t>
+    <t>2026-09-14T19:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/ValueSet-mii-vs-consent-policy.xlsx
+++ b/branches/release/v2027.0.0-ballot/ValueSet-mii-vs-consent-policy.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:07:39+00:00</t>
+    <t>2026-09-14T19:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
